--- a/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 학교에서 풍선을 보면—복도 건너편에서 보이기만 해도—가슴이 바로 조여오고 잠깐 그 자리에서 얼어붙어요. 제가 뭘 해야 하는지 다시 제대로 생각할 수 있게 되기까지 시간이 좀 걸려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 풍선 외에 다른 것에도 이런 반응을 보이시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 다른 건 딱히 없어요. 주로 풍선이에요. 교실에 풍선이 있으면 대부분 그냥 장식이라는 걸 알긴 하는데, 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠다니고 있으면, 제 얼굴 바로 앞에서 터질 수도 있다는 생각이 들어요. 실제로 그럴 만한 것보다 더 무섭게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 풍선에 대한 이런 반응을 얼마나 오래 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 지금 한 일곱 달 정도 됐어요. 어린이 미술 축제 도중에 풍선이 제 얼굴 아주 가까이에서 터진 뒤부터 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 풍선을 볼 수도 있는 장소나 상황을 피하게 되는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 요즘엔 가능하면 피하려고 하고 있어요. 학교에서는 풍선이 있으면 보조교사들한테 생일 파티 진행을 맡기거나, 근처에 풍선이 있는 축제 부스에서 멀리 떨어져요. 꼭 있어야 하는 상황이면, 거리를 두고 그냥 풍선을 안 보려고 하면서 버텨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 풍선에 대한 이런 반응이 일상생활이나 인간관계에 상당한 고통이나 문제를 일으키고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 그래요. 업무에 영향을 주기 시작했어요. 풍선이 있는 평소 교실 축하 행사를 보조교사들한테 넘겨야 했고, 계획했던 축제 미술 테이블 참여를 놓쳤어요, 근처에 풍선이 있어서요. 상사도 알아챘고, 그래서… 문제가 되고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 풍선이 터지던 순간의 기억이나 장면이 아주 생생하고 괴롭게 떠오르는 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까, 그런 일이 있었다는 건 기억하는데, 터지는 장면이 생생하게 떠오르거나 그러지는 않아요. 그보다는 지금 풍선을 보면 정말 긴장하게 되는 쪽에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 풍선이 터지지 않을 걸 알면서도 풍선을 보면 압도적인 두려움을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 아마 그냥 장식일 뿐이고 아무 일도 없을 거라는 걸 알면서도, 풍선이 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠 있는 걸 보면 무서워져요. 제 얼굴 바로 앞에서 터질 것 같은 느낌이 들고, 그 두려움이 상황에 비해 너무 큰 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 풍선을 볼 때 공황발작 같은 걸 겪는다고 느끼신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 그것과 비슷하게 느껴질 때가 있어요. 학교에서 풍선을 발견하는 순간, 복도 건너편이라 해도, 가슴이 조여오고 잠깐 얼어붙어요. 제가 뭘 해야 하는지 명료하게 생각할 수 있게 되기까지 시간이 좀 걸려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 풍선 외에, 풍선이 터졌던 사건을 떠올리게 해서 피하는 다른 상황이나 물건이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 딱히 없어요. 그 일 때문에 피하는 다른 물건이나 상황은 떠오르지 않아요. 주로 풍선 자체예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 풍선이 얼굴 근처에서 터진 그 순간을 다시 겪고 있는 것처럼 느껴지는 플래시백이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그 순간으로 돌아간 느낌은 딱히 안 들어요. 그보다는 풍선을 보면 긴장되고 또 그런 일이 생길까 봐 걱정되는 쪽에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 풍선에 대한 두려움이 실제 위험에 비해 과도하다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 그렇게 생각해요. 교실에 있는 풍선은 논리적으로 대부분 그냥 장식이고 그렇게 위험한 게 아니라는 걸 알아요. 근데 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠 있으면, 곧바로 제 얼굴 바로 앞에서 터질 수도 있다는 생각이 들고, 상황에 비해 훨씬 더 무서워져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 풍선에 대한 두려움이 친구나 가족, 동료와의 관계에 영향을 미쳤나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 주로 직장에서요. 풍선이 있는 평소 교실 축하 행사를 보조교사들한테 넘겨야 했고, 계획했던 축제 미술 테이블 참여도 놓쳤어요. 상사도 알아챘고, 그래서 그쪽에서 영향을 주기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 안전하고 통제된 환경에서 풍선에 맞서거나 노출된다면 풍선에 대한 두려움이 나아질 것 같다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 정말 점진적이고 통제된 방식이라면 도움이 될 수도 있겠다는 생각은 드는데, 그걸 해본다는 생각 자체가 여전히 긴장돼요. 정식으로 시도해본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 풍선이 터진 사건이 본인에게 특별히 트라우마적이었다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 그런 것 같아요. 그 이후로 정말 계속 이어져 왔어요—지금 한 일곱 달 정도요—어린이 미술 축제 도중 풍선이 제 얼굴 가까이에서 터진 뒤부터요. 그 순간이 어떻게 보면 계속 남아 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 그곳에 풍선이 있을까 봐 두려워서 사교 모임을 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네, 풍선이 있을 것 같으면 피하려고 하거나 그 자리에서 멀리 떨어져 있으려고 해요. 요즘엔 보조교사들한테 생일 파티 진행을 부탁하고, 축제에서는 근처에 풍선이 있는 테이블에서 멀어져요. 꼭 있어야 한다면 거리를 두고 그냥 풍선을 안 보려고 하면서 버텨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 원치 않는데도 풍선이 터진 사건을 자주 생각하게 되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 자주라고는 못 하겠어요. 뭔가 그때를 떠올리게 하면 가끔 생각나긴 하는데, 원치 않는데도 항상 그 생각을 하고 있는 건 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 다른 나쁜 일이나 무서운 일이 또 생길까 봐 자주 걱정하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 일반적인 방식으로는 딱히 그렇지 않아요. 그러니까, 저를 놀라게 할 것 같은 특정 상황에 대해서는 걱정하는데, 평소에 뭔가 나쁜 일이 저한테 생길 거라고 생각하면서 다니지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 풍선이 터지는 것에 대한 원치 않는 기억이나 이미지가 머릿속에 떠오르는 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 가끔요, 네, 뭔가 그걸 떠올리게 하면요. 계속 일어나는 건 아닌데, 터지는 장면이 순간적으로 머릿속에 떠오를 때가 있고, 그러면 그 생각을 밀어내려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 풍선이 터진 사건에 대해 생각하거나 이야기하는 걸 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 잘 모르겠어요. 제가 먼저 그 얘기를 꺼내지는 않는데, 그렇다고 항상 적극적으로 이야기를 피한다고도 말 못 하겠어요. 얘기가 나오면 대답은 할 수 있는데, 굳이 곱씹고 싶지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 특정공포증 (D012)
 인구통계: 성별 여성 / 나이 30 / 직업상태 preschool or kindergarten teacher / 최종학력 학사
@@ -575,467 +978,33 @@
 증상 지속 기간: 7 months
 추가 요건: 
 주호소 증상 코드: S063
-배경 서술: 얼린은 최근 자신의 직업적 이미지와 지역사회 활동에 좀 더 의도적으로 신경 쓰려고 노력하며, 학교 행사에 더 많이 참여하고 리더십 역할에 맞게 옷을 갖춰 입고, 축제 성격의 교실 활동을 주도해왔다. 어린이 미술 축제 도중 풍선이 얼굴 가까이에서 터진 이후, 풍선에 대한 그녀의 불안감은 점차 7개월에 걸쳐 하나의 패턴으로 굳어져, 풍선 장식을 보는 것만으로도 즉각적인 두려움을 느끼게 되었고, 실제 위험이 미미하다는 걸 알면서도 생일 파티 자리나 축제 부스, 풍선을 사용하는 교실 전시 등을 피하기 시작했다. 정기적인 축하 행사를 보조교사들에게 맡겨야 하고, 자신이 직접 기획을 도왔던 문화 축제 미술 테이블에 풍선이 근처에 있다는 이유로 참여하지 못하게 되면서 문제는 임상적으로 유의미해졌다. 상사가 이 회피 행동이 수업 업무에 지장을 주고 있다는 것을 알아채면서, 그녀는 학교 직원 복지 서비스를 통해 정신과 평가를 의뢰받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 학교에서 풍선을 보면—복도 건너편에서 보이기만 해도—가슴이 바로 조여오고 잠깐 그 자리에서 얼어붙어요. 제가 뭘 해야 하는지 다시 제대로 생각할 수 있게 되기까지 시간이 좀 걸려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 풍선 외에 다른 것에도 이런 반응을 보이시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 다른 건 딱히 없어요. 주로 풍선이에요. 교실에 풍선이 있으면 대부분 그냥 장식이라는 걸 알긴 하는데, 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠다니고 있으면, 제 얼굴 바로 앞에서 터질 수도 있다는 생각이 들어요. 실제로 그럴 만한 것보다 더 무섭게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 풍선에 대한 이런 반응을 얼마나 오래 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 지금 한 일곱 달 정도 됐어요. 어린이 미술 축제 도중에 풍선이 제 얼굴 아주 가까이에서 터진 뒤부터 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 풍선을 볼 수도 있는 장소나 상황을 피하게 되는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 요즘엔 가능하면 피하려고 하고 있어요. 학교에서는 풍선이 있으면 보조교사들한테 생일 파티 진행을 맡기거나, 근처에 풍선이 있는 축제 부스에서 멀리 떨어져요. 꼭 있어야 하는 상황이면, 거리를 두고 그냥 풍선을 안 보려고 하면서 버텨요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 풍선에 대한 이런 반응이 일상생활이나 인간관계에 상당한 고통이나 문제를 일으키고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 그래요. 업무에 영향을 주기 시작했어요. 풍선이 있는 평소 교실 축하 행사를 보조교사들한테 넘겨야 했고, 계획했던 축제 미술 테이블 참여를 놓쳤어요, 근처에 풍선이 있어서요. 상사도 알아챘고, 그래서… 문제가 되고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 풍선이 터지던 순간의 기억이나 장면이 아주 생생하고 괴롭게 떠오르는 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까, 그런 일이 있었다는 건 기억하는데, 터지는 장면이 생생하게 떠오르거나 그러지는 않아요. 그보다는 지금 풍선을 보면 정말 긴장하게 되는 쪽에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 풍선이 터지지 않을 걸 알면서도 풍선을 보면 압도적인 두려움을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 아마 그냥 장식일 뿐이고 아무 일도 없을 거라는 걸 알면서도, 풍선이 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠 있는 걸 보면 무서워져요. 제 얼굴 바로 앞에서 터질 것 같은 느낌이 들고, 그 두려움이 상황에 비해 너무 큰 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 풍선을 볼 때 공황발작 같은 걸 겪는다고 느끼신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 그것과 비슷하게 느껴질 때가 있어요. 학교에서 풍선을 발견하는 순간, 복도 건너편이라 해도, 가슴이 조여오고 잠깐 얼어붙어요. 제가 뭘 해야 하는지 명료하게 생각할 수 있게 되기까지 시간이 좀 걸려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 풍선 외에, 풍선이 터졌던 사건을 떠올리게 해서 피하는 다른 상황이나 물건이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 딱히 없어요. 그 일 때문에 피하는 다른 물건이나 상황은 떠오르지 않아요. 주로 풍선 자체예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 풍선이 얼굴 근처에서 터진 그 순간을 다시 겪고 있는 것처럼 느껴지는 플래시백이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 그 순간으로 돌아간 느낌은 딱히 안 들어요. 그보다는 풍선을 보면 긴장되고 또 그런 일이 생길까 봐 걱정되는 쪽에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 풍선에 대한 두려움이 실제 위험에 비해 과도하다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 그렇게 생각해요. 교실에 있는 풍선은 논리적으로 대부분 그냥 장식이고 그렇게 위험한 게 아니라는 걸 알아요. 근데 팽팽하게 부풀어 있거나 아이들 근처에서 둥둥 떠 있으면, 곧바로 제 얼굴 바로 앞에서 터질 수도 있다는 생각이 들고, 상황에 비해 훨씬 더 무서워져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 풍선에 대한 두려움이 친구나 가족, 동료와의 관계에 영향을 미쳤나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 주로 직장에서요. 풍선이 있는 평소 교실 축하 행사를 보조교사들한테 넘겨야 했고, 계획했던 축제 미술 테이블 참여도 놓쳤어요. 상사도 알아챘고, 그래서 그쪽에서 영향을 주기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 안전하고 통제된 환경에서 풍선에 맞서거나 노출된다면 풍선에 대한 두려움이 나아질 것 같다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 정말 점진적이고 통제된 방식이라면 도움이 될 수도 있겠다는 생각은 드는데, 그걸 해본다는 생각 자체가 여전히 긴장돼요. 정식으로 시도해본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 풍선이 터진 사건이 본인에게 특별히 트라우마적이었다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 그런 것 같아요. 그 이후로 정말 계속 이어져 왔어요—지금 한 일곱 달 정도요—어린이 미술 축제 도중 풍선이 제 얼굴 가까이에서 터진 뒤부터요. 그 순간이 어떻게 보면 계속 남아 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 그곳에 풍선이 있을까 봐 두려워서 사교 모임을 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네, 풍선이 있을 것 같으면 피하려고 하거나 그 자리에서 멀리 떨어져 있으려고 해요. 요즘엔 보조교사들한테 생일 파티 진행을 부탁하고, 축제에서는 근처에 풍선이 있는 테이블에서 멀어져요. 꼭 있어야 한다면 거리를 두고 그냥 풍선을 안 보려고 하면서 버텨요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 원치 않는데도 풍선이 터진 사건을 자주 생각하게 되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 자주라고는 못 하겠어요. 뭔가 그때를 떠올리게 하면 가끔 생각나긴 하는데, 원치 않는데도 항상 그 생각을 하고 있는 건 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 다른 나쁜 일이나 무서운 일이 또 생길까 봐 자주 걱정하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 일반적인 방식으로는 딱히 그렇지 않아요. 그러니까, 저를 놀라게 할 것 같은 특정 상황에 대해서는 걱정하는데, 평소에 뭔가 나쁜 일이 저한테 생길 거라고 생각하면서 다니지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 풍선이 터지는 것에 대한 원치 않는 기억이나 이미지가 머릿속에 떠오르는 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 가끔요, 네, 뭔가 그걸 떠올리게 하면요. 계속 일어나는 건 아닌데, 터지는 장면이 순간적으로 머릿속에 떠오를 때가 있고, 그러면 그 생각을 밀어내려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 풍선이 터진 사건에 대해 생각하거나 이야기하는 걸 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 잘 모르겠어요. 제가 먼저 그 얘기를 꺼내지는 않는데, 그렇다고 항상 적극적으로 이야기를 피한다고도 말 못 하겠어요. 얘기가 나오면 대답은 할 수 있는데, 굳이 곱씹고 싶지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 얼린은 최근 자신의 직업적 이미지와 지역사회 활동에 좀 더 의도적으로 신경 쓰려고 노력하며, 학교 행사에 더 많이 참여하고 리더십 역할에 맞게 옷을 갖춰 입고, 축제 성격의 교실 활동을 주도해왔다. 어린이 미술 축제 도중 풍선이 얼굴 가까이에서 터진 이후, 풍선에 대한 그녀의 불안감은 점차 7개월에 걸쳐 하나의 패턴으로 굳어져, 풍선 장식을 보는 것만으로도 즉각적인 두려움을 느끼게 되었고, 실제 위험이 미미하다는 걸 알면서도 생일 파티 자리나 축제 부스, 풍선을 사용하는 교실 전시 등을 피하기 시작했다. 정기적인 축하 행사를 보조교사들에게 맡겨야 하고, 자신이 직접 기획을 도왔던 문화 축제 미술 테이블에 풍선이 근처에 있다는 이유로 참여하지 못하게 되면서 문제는 임상적으로 유의미해졌다. 상사가 이 회피 행동이 수업 업무에 지장을 주고 있다는 것을 알아채면서, 그녀는 학교 직원 복지 서비스를 통해 정신과 평가를 의뢰받았다.
+표집된 증상 목록:
+  - S062 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - S063 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
+  - S064 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 특정공포증 (D012) | 배제됨: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.231)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).; 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.; 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.231)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
+  - 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1000,11 +1005,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
